--- a/output/full_scan/batch_seq0_2026-07-03.xlsx
+++ b/output/full_scan/batch_seq0_2026-07-03.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O116"/>
+  <dimension ref="A1:O117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -845,21 +845,21 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>8093</v>
+        <v>8096</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>708.3690909675195</v>
+        <v>739.2363497176024</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>20.5</v>
+        <v>157.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>55.64311796157857</v>
+        <v>64.78321968344051</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>9.549741569402688</v>
+        <v>35.27012510063626</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>4.00322845402316</v>
+        <v>0.271099912642834</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2499803718368138</v>
+        <v>-0.502941165025252</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>8150</v>
+        <v>8093</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>689.5656366828812</v>
+        <v>708.3690909675195</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>105</v>
+        <v>20.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>55.60959256752573</v>
+        <v>55.64311796157857</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>27.7538894552991</v>
+        <v>9.549741569402688</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.6373977721668426</v>
+        <v>4.00322845402316</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.0035896794920593</v>
+        <v>0.2499803718368138</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8222</v>
+        <v>8150</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>663.8748662450024</v>
+        <v>689.5656366828812</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>44.75</v>
+        <v>105</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>74.46979986304645</v>
+        <v>55.60959256752573</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>21.45738251898058</v>
+        <v>27.7538894552991</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>4.48748662450024</v>
+        <v>0.6373977721668426</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.9349068522875436</v>
+        <v>0.0035896794920593</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>9905</v>
+        <v>8222</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>大華</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>656.9269672759555</v>
+        <v>663.8748662450024</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>21.35</v>
+        <v>44.75</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>64.82671358857741</v>
+        <v>74.46979986304645</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>22.041721662116</v>
+        <v>21.45738251898058</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.9926967275955474</v>
+        <v>4.48748662450024</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.0456033493522649</v>
+        <v>0.9349068522875436</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>8926</v>
+        <v>9905</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>大華</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>652.0709884940518</v>
+        <v>656.9269672759555</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>75</v>
+        <v>21.35</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>55.17451899437584</v>
+        <v>64.82671358857741</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>42.4051741161282</v>
+        <v>22.041721662116</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.4805698538538593</v>
+        <v>0.9926967275955474</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-1.284632385919229</v>
+        <v>0.0456033493522649</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8064</v>
+        <v>8926</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>647.8866899860355</v>
+        <v>652.0709884940518</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>145.5</v>
+        <v>75</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>51.95509883245478</v>
+        <v>55.17451899437584</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>25.61390024933449</v>
+        <v>42.4051741161282</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.4105957044977134</v>
+        <v>0.4805698538538593</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-1.841589789918626</v>
+        <v>-1.284632385919229</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8499</v>
+        <v>8064</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>647.3569445009718</v>
+        <v>647.8866899860355</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>315</v>
+        <v>145.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,49 +1188,49 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>56.62095390385872</v>
+        <v>51.95509883245478</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>16.0670170874236</v>
+        <v>25.61390024933449</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.9319245062016748</v>
+        <v>0.4105957044977134</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.1613306509777334</v>
+        <v>-1.841589789918626</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, hist_turn_positive, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>8466</v>
+        <v>8499</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>642.5066242205548</v>
+        <v>647.3569445009718</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>17.4</v>
+        <v>315</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>65.86226294142946</v>
+        <v>56.62095390385872</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>22.49443401472955</v>
+        <v>16.0670170874236</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.524936579211134</v>
+        <v>0.9319245062016748</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.182331357621988</v>
+        <v>0.1613306509777334</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, hist_turn_positive, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8121</v>
+        <v>8466</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>629.4671764069873</v>
+        <v>642.5066242205548</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>48.3</v>
+        <v>17.4</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>56.1940166155112</v>
+        <v>65.86226294142946</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>34.03587807237746</v>
+        <v>22.49443401472955</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.7338818376858243</v>
+        <v>1.524936579211134</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.5652654109551793</v>
+        <v>0.182331357621988</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8162</v>
+        <v>8121</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>625.9502661802183</v>
+        <v>629.4671764069873</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>79.2</v>
+        <v>48.3</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>57.10456869196818</v>
+        <v>56.1940166155112</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>38.13508077489596</v>
+        <v>34.03587807237746</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.5852559331307038</v>
+        <v>0.7338818376858243</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.6730669407687238</v>
+        <v>-0.5652654109551793</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8462</v>
+        <v>8162</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>601.3973279267391</v>
+        <v>625.9502661802183</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>147</v>
+        <v>79.2</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>61.37821324547864</v>
+        <v>57.10456869196818</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>20.02254008530952</v>
+        <v>38.13508077489596</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.215867212900119</v>
+        <v>0.5852559331307038</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.7601091899097527</v>
+        <v>-0.6730669407687238</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8411</v>
+        <v>8462</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>600.143505110993</v>
+        <v>601.3973279267391</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>12.35</v>
+        <v>147</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>58.60539529601563</v>
+        <v>61.37821324547864</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>35.89570303776357</v>
+        <v>20.02254008530952</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.4111296711563401</v>
+        <v>1.215867212900119</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.0274116304228499</v>
+        <v>0.7601091899097527</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8163</v>
+        <v>8411</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>598.6601884675138</v>
+        <v>600.143505110993</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>41</v>
+        <v>12.35</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>51.40536564955218</v>
+        <v>58.60539529601563</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>34.54478714885951</v>
+        <v>35.89570303776357</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.231940349945743</v>
+        <v>0.4111296711563401</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.6863006735350938</v>
+        <v>0.0274116304228499</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>8481</v>
+        <v>8163</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>589.0205444917801</v>
+        <v>598.6601884675138</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>42.1</v>
+        <v>41</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>61.3669089052954</v>
+        <v>51.40536564955218</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>20.52366255014795</v>
+        <v>34.54478714885951</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.823425796798441</v>
+        <v>0.231940349945743</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.0210180654750131</v>
+        <v>-0.6863006735350938</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8088</v>
+        <v>8481</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>585.7353242777598</v>
+        <v>589.0205444917801</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>59.8</v>
+        <v>42.1</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>45.72360544467358</v>
+        <v>61.3669089052954</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>21.09394454210312</v>
+        <v>20.52366255014795</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.2630830878032196</v>
+        <v>1.823425796798441</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.9782658138243568</v>
+        <v>-0.0210180654750131</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8105</v>
+        <v>8088</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>584.60313956108</v>
+        <v>585.7353242777598</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>21.75</v>
+        <v>59.8</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>53.61046407117093</v>
+        <v>45.72360544467358</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>37.26556658716538</v>
+        <v>21.09394454210312</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.2491830714445088</v>
+        <v>0.2630830878032196</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.3063552000692549</v>
+        <v>-0.9782658138243568</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8215</v>
+        <v>8105</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>568.2218520704166</v>
+        <v>584.60313956108</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>29.5</v>
+        <v>21.75</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>50.20060361370946</v>
+        <v>53.61046407117093</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>22.91781463572436</v>
+        <v>37.26556658716538</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.3855076081574349</v>
+        <v>0.2491830714445088</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,7 +1736,7 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.1508762983258199</v>
+        <v>-0.3063552000692549</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8358</v>
+        <v>8215</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>566.2336897923448</v>
+        <v>568.2218520704166</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>590</v>
+        <v>29.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>51.30106615107151</v>
+        <v>50.20060361370946</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>17.29493727161371</v>
+        <v>22.91781463572436</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.036395629820385</v>
+        <v>0.3855076081574349</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-13.07703202897893</v>
+        <v>-0.1508762983258199</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8476</v>
+        <v>8358</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>560.3471606991149</v>
+        <v>566.2336897923448</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>24.45</v>
+        <v>590</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>82.46333623290352</v>
+        <v>51.30106615107151</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>61.55510560220575</v>
+        <v>17.29493727161371</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.5102419405437608</v>
+        <v>1.036395629820385</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.2268839186358207</v>
+        <v>-13.07703202897893</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8049</v>
+        <v>8476</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>547.1586319108859</v>
+        <v>560.3471606991149</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>27.25</v>
+        <v>24.45</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>51.80650762783336</v>
+        <v>82.46333623290352</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>27.09745025230344</v>
+        <v>61.55510560220575</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.25303325225888</v>
+        <v>0.5102419405437608</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.0711904951628531</v>
+        <v>0.2268839186358207</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8071</v>
+        <v>8049</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>544.588837542113</v>
+        <v>547.1586319108859</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>32.55</v>
+        <v>27.25</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>66.34399404828163</v>
+        <v>51.80650762783336</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45.91278994053447</v>
+        <v>27.09745025230344</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.5548523319712871</v>
+        <v>1.25303325225888</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.2846072026198403</v>
+        <v>-0.0711904951628531</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8081</v>
+        <v>8071</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>533.9071471300697</v>
+        <v>544.588837542113</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>319.5</v>
+        <v>32.55</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>59.61447534027155</v>
+        <v>66.34399404828163</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>24.29430772114004</v>
+        <v>45.91278994053447</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.003049863718437</v>
+        <v>0.5548523319712871</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.0469261441947139</v>
+        <v>0.2846072026198403</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -2011,21 +2011,21 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8438</v>
+        <v>8081</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>532.3379788424796</v>
+        <v>533.9071471300697</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>100.5</v>
+        <v>319.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>61.92117657571863</v>
+        <v>59.61447534027155</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>28.22613605982985</v>
+        <v>24.29430772114004</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.5245637186007531</v>
+        <v>1.003049863718437</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>1.292228046554679</v>
+        <v>-0.0469261441947139</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8442</v>
+        <v>8438</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>531.383789695641</v>
+        <v>532.3379788424796</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>42.95</v>
+        <v>100.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>57.9462926424216</v>
+        <v>61.92117657571863</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>25.27711594027377</v>
+        <v>28.22613605982985</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.5728204514698639</v>
+        <v>0.5245637186007531</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.4887568895288463</v>
+        <v>1.292228046554679</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8054</v>
+        <v>8442</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>529.3830110785763</v>
+        <v>531.383789695641</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>113.5</v>
+        <v>42.95</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>51.70956138338126</v>
+        <v>57.9462926424216</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>23.30486024593325</v>
+        <v>25.27711594027377</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.6873091643172858</v>
+        <v>0.5728204514698639</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.0185056635765437</v>
+        <v>0.4887568895288463</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>8072</v>
+        <v>8054</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>524.4758401161562</v>
+        <v>529.3830110785763</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>30.25</v>
+        <v>113.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>57.26607532341556</v>
+        <v>51.70956138338126</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>23.80322242803386</v>
+        <v>23.30486024593325</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.150673650919875</v>
+        <v>0.6873091643172858</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.026359158040315</v>
+        <v>0.0185056635765437</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8261</v>
+        <v>8072</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>富鼎</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>522.2755872035384</v>
+        <v>524.4758401161562</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>320</v>
+        <v>30.25</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>78.07192140843476</v>
+        <v>57.26607532341556</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>50.98131844114868</v>
+        <v>23.80322242803386</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>2.471944963755382</v>
+        <v>1.150673650919875</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>9.720529031099076</v>
+        <v>-0.026359158040315</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8422</v>
+        <v>8261</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>512.1309291725128</v>
+        <v>522.2755872035384</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>28.35</v>
+        <v>320</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>52.02944182984372</v>
+        <v>78.07192140843476</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>13.63203860374261</v>
+        <v>50.98131844114868</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>2.54384941727168</v>
+        <v>2.471944963755382</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.1316520626184237</v>
+        <v>9.720529031099076</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, williams_r_recovery</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8050</v>
+        <v>8422</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>503.0967945521223</v>
+        <v>512.1309291725128</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>55.9</v>
+        <v>28.35</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>55.74745937114608</v>
+        <v>52.02944182984372</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>26.8208376243054</v>
+        <v>13.63203860374261</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.7181798655181395</v>
+        <v>2.54384941727168</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.4381063695993398</v>
+        <v>-0.1316520626184237</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8076</v>
+        <v>8050</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>501.3115553872533</v>
+        <v>503.0967945521223</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>26</v>
+        <v>55.9</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>56.2066654416197</v>
+        <v>55.74745937114608</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>14.49044916984553</v>
+        <v>26.8208376243054</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.5521994506356851</v>
+        <v>0.7181798655181395</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.1161288177230228</v>
+        <v>-0.4381063695993398</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8277</v>
+        <v>8076</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>499.4269159630919</v>
+        <v>501.3115553872533</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>9.09</v>
+        <v>26</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>44.11091448399007</v>
+        <v>56.2066654416197</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>24.04438585967199</v>
+        <v>14.49044916984553</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.4377251867846034</v>
+        <v>0.5521994506356851</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.2671948857552046</v>
+        <v>-0.1161288177230228</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8374</v>
+        <v>8277</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>498.780989359624</v>
+        <v>499.4269159630919</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>92.7</v>
+        <v>9.09</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>51.70086629114972</v>
+        <v>44.11091448399007</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>14.37926487669273</v>
+        <v>24.04438585967199</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>3.544347705633396</v>
+        <v>0.4377251867846034</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.1566260203961789</v>
+        <v>-0.2671948857552046</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, hist_turn_positive, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8289</v>
+        <v>8374</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>泰藝</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>494.6639350384188</v>
+        <v>498.780989359624</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>65.59999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>54.80614387245142</v>
+        <v>51.70086629114972</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>20.49006154277122</v>
+        <v>14.37926487669273</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.387784049786698</v>
+        <v>3.544347705633396</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.6478259212116124</v>
+        <v>0.1566260203961789</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, hist_turn_positive, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8131</v>
+        <v>8289</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>489.0948617167269</v>
+        <v>494.6639350384188</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>74.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>55.66176382646065</v>
+        <v>54.80614387245142</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>12.48430866857718</v>
+        <v>20.49006154277122</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.8575809806672615</v>
+        <v>1.387784049786698</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.4823428483169547</v>
+        <v>-0.6478259212116124</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8227</v>
+        <v>8131</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>488.6966055392147</v>
+        <v>489.0948617167269</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>208</v>
+        <v>74.8</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,49 +2672,49 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>55.44737901800807</v>
+        <v>55.66176382646065</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>15.98544193500586</v>
+        <v>12.48430866857718</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.671727173931523</v>
+        <v>0.8575809806672615</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>2.615206149049691</v>
+        <v>-0.4823428483169547</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8112</v>
+        <v>8227</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>488.3345399136165</v>
+        <v>488.6966055392147</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>92.90000000000001</v>
+        <v>208</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,49 +2725,49 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>51.44846375955306</v>
+        <v>55.44737901800807</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>20.23598785455772</v>
+        <v>15.98544193500586</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.009592963849015</v>
+        <v>1.671727173931523</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.9643614231761348</v>
+        <v>2.615206149049691</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8473</v>
+        <v>8112</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>487.9893282344681</v>
+        <v>488.3345399136165</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>49.15</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>52.4549727560019</v>
+        <v>51.44846375955306</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>23.95277643024474</v>
+        <v>20.23598785455772</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.5306854818151979</v>
+        <v>1.009592963849015</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.707505447218943</v>
+        <v>-0.9643614231761348</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8110</v>
+        <v>8473</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>483.569079283838</v>
+        <v>487.9893282344681</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>53.7</v>
+        <v>49.15</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>45.82085137449796</v>
+        <v>52.4549727560019</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>16.95736290978275</v>
+        <v>23.95277643024474</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.268016928048177</v>
+        <v>0.5306854818151979</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.7811520230243909</v>
+        <v>-0.707505447218943</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>9136</v>
+        <v>8110</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>479.5912647769405</v>
+        <v>483.569079283838</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>13.6</v>
+        <v>53.7</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>49.1004375165861</v>
+        <v>45.82085137449796</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>35.99901317358435</v>
+        <v>16.95736290978275</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.1836891739299843</v>
+        <v>0.268016928048177</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.6879802965747381</v>
+        <v>-0.7811520230243909</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8111</v>
+        <v>9136</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>479.5462143817888</v>
+        <v>479.5912647769405</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>53.3</v>
+        <v>13.6</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>39.37827413562268</v>
+        <v>49.1004375165861</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>25.71194712716671</v>
+        <v>35.99901317358435</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.4880251596569126</v>
+        <v>0.1836891739299843</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.052880324681678</v>
+        <v>-0.6879802965747381</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8092</v>
+        <v>8111</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>478.2969921629027</v>
+        <v>479.5462143817888</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>14.7</v>
+        <v>53.3</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>48.31253903339305</v>
+        <v>39.37827413562268</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>20.12571629339273</v>
+        <v>25.71194712716671</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>2.430169530889859</v>
+        <v>0.4880251596569126</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.0018682650574272</v>
+        <v>0.052880324681678</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, hist_turn_positive, foreign_buy_3d, adx_trending, williams_r_recovery</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8171</v>
+        <v>8092</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>478.0424243008933</v>
+        <v>478.2969921629027</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>21.4</v>
+        <v>14.7</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>45.0892407688879</v>
+        <v>48.31253903339305</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>20.0637573638173</v>
+        <v>20.12571629339273</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.4723175634060009</v>
+        <v>2.430169530889859</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.007982670434900399</v>
+        <v>0.0018682650574272</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, foreign_buy_3d, adx_trending, kd_golden_cross</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, hist_turn_positive, foreign_buy_3d, adx_trending, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>9105</v>
+        <v>8171</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>470.9121767581741</v>
+        <v>478.0424243008933</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>21.4</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>51.97338715992261</v>
+        <v>45.0892407688879</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>33.99319293873612</v>
+        <v>20.0637573638173</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.2699845524157716</v>
+        <v>0.4723175634060009</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.1726584082788858</v>
+        <v>0.007982670434900399</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>9902</v>
+        <v>9105</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>台火</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>449.4321330874823</v>
+        <v>470.9121767581741</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>14.25</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>60.06111601147363</v>
+        <v>51.97338715992261</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>14.79196456155776</v>
+        <v>33.99319293873612</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>2.555539667523313</v>
+        <v>0.2699845524157716</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.0541056808762756</v>
+        <v>-0.1726584082788858</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8454</v>
+        <v>9902</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>台火</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>445.9738987999084</v>
+        <v>449.4321330874823</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>293</v>
+        <v>14.25</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>48.20817809769094</v>
+        <v>60.06111601147363</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>38.79405045591695</v>
+        <v>14.79196456155776</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.7038963008400076</v>
+        <v>2.555539667523313</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-12.47906564893762</v>
+        <v>0.0541056808762756</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8097</v>
+        <v>8454</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>442.3421328608147</v>
+        <v>445.9738987999084</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>58</v>
+        <v>293</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>48.51838381982808</v>
+        <v>48.20817809769094</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>19.46361063599478</v>
+        <v>38.79405045591695</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>3.253120341472448</v>
+        <v>0.7038963008400076</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.3250421618448391</v>
+        <v>-12.47906564893762</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8234</v>
+        <v>8097</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>442.2865998597994</v>
+        <v>442.3421328608147</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>54.61512743000523</v>
+        <v>48.51838381982808</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>22.8779323715451</v>
+        <v>19.46361063599478</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.008042420688985</v>
+        <v>3.253120341472448</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.7363186836676769</v>
+        <v>-0.3250421618448391</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8240</v>
+        <v>8234</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>438.8999073296896</v>
+        <v>442.2865998597994</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>52.6</v>
+        <v>71</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>39.64709200288394</v>
+        <v>54.61512743000523</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>16.2317819099302</v>
+        <v>22.8779323715451</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.3010027763591419</v>
+        <v>1.008042420688985</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.1714179566854565</v>
+        <v>0.7363186836676769</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8201</v>
+        <v>8240</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>434.2044383724067</v>
+        <v>438.8999073296896</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>13.4</v>
+        <v>52.6</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>53.18978098358534</v>
+        <v>39.64709200288394</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>18.30466905013139</v>
+        <v>16.2317819099302</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.964896498921446</v>
+        <v>0.3010027763591419</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.0282855341485381</v>
+        <v>-0.1714179566854565</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8155</v>
+        <v>8201</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>428.4958410225156</v>
+        <v>434.2044383724067</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>384.5</v>
+        <v>13.4</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>50.30220069343469</v>
+        <v>53.18978098358534</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>15.73514513652134</v>
+        <v>18.30466905013139</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.5973704714359959</v>
+        <v>0.964896498921446</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.2435085775181451</v>
+        <v>-0.0282855341485381</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>8074</v>
+        <v>8155</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>421.0711908221911</v>
+        <v>428.4958410225156</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>69.5</v>
+        <v>384.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>46.2617966727618</v>
+        <v>50.30220069343469</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>11.72061309342483</v>
+        <v>15.73514513652134</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.5914833219202236</v>
+        <v>0.5973704714359959</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.3263799152800712</v>
+        <v>-0.2435085775181451</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8291</v>
+        <v>8074</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>尚茂</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>420.444036968697</v>
+        <v>421.0711908221911</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>37.2</v>
+        <v>69.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>36.35072469587908</v>
+        <v>46.2617966727618</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>26.70059056915082</v>
+        <v>11.72061309342483</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.6628249158737253</v>
+        <v>0.5914833219202236</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-1.409889443763092</v>
+        <v>-0.3263799152800712</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>8443</v>
+        <v>8291</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>418.6737059634348</v>
+        <v>420.444036968697</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>11.5</v>
+        <v>37.2</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>54.46703721205446</v>
+        <v>36.35072469587908</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>49.07498730183332</v>
+        <v>26.70059056915082</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.667370596343479</v>
+        <v>0.6628249158737253</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.0172105402257876</v>
+        <v>-1.409889443763092</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8070</v>
+        <v>8443</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>416.2398928113166</v>
+        <v>418.6737059634348</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>56</v>
+        <v>11.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>53.57398951022777</v>
+        <v>54.46703721205446</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>21.91362477048185</v>
+        <v>49.07498730183332</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.4467500140700139</v>
+        <v>0.667370596343479</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.516745586351369</v>
+        <v>0.0172105402257876</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8488</v>
+        <v>8070</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>414.28033597907</v>
+        <v>416.2398928113166</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>10.2</v>
+        <v>56</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>51.83995077780085</v>
+        <v>53.57398951022777</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>14.60749513048846</v>
+        <v>21.91362477048185</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.498483523761632</v>
+        <v>0.4467500140700139</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.07224573155301429</v>
+        <v>-0.516745586351369</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8086</v>
+        <v>8488</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>413.6894108829986</v>
+        <v>414.28033597907</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>144</v>
+        <v>10.2</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>43.15397256892869</v>
+        <v>51.83995077780085</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>14.73763844831124</v>
+        <v>14.60749513048846</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.5396819092093057</v>
+        <v>0.498483523761632</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-1.63547230124167</v>
+        <v>-0.07224573155301429</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>9911</v>
+        <v>8086</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>櫻花</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>411.2921869701883</v>
+        <v>413.6894108829986</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>85.2</v>
+        <v>144</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>62.2905392643172</v>
+        <v>43.15397256892869</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>12.31485117884677</v>
+        <v>14.73763844831124</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.342733633329739</v>
+        <v>0.5396819092093057</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.1646844193613867</v>
+        <v>-1.63547230124167</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8932</v>
+        <v>9911</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>櫻花</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>410.7195816795277</v>
+        <v>411.2921869701883</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>105.5</v>
+        <v>85.2</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>52.88772096081645</v>
+        <v>62.2905392643172</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>21.08901823344407</v>
+        <v>12.31485117884677</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.4719581679527697</v>
+        <v>1.342733633329739</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.1741455078274856</v>
+        <v>0.1646844193613867</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8183</v>
+        <v>8932</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>409.999099340555</v>
+        <v>410.7195816795277</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>34.7</v>
+        <v>105.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>60.14097494455193</v>
+        <v>52.88772096081645</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>23.38373024466184</v>
+        <v>21.08901823344407</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.7999099340555008</v>
+        <v>0.4719581679527697</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.318547725271222</v>
+        <v>0.1741455078274856</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8390</v>
+        <v>8183</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>406.3323950058719</v>
+        <v>409.999099340555</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>109</v>
+        <v>34.7</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>47.0745128137694</v>
+        <v>60.14097494455193</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>21.19482262142719</v>
+        <v>23.38373024466184</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.420501989814022</v>
+        <v>0.7999099340555008</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-1.100709063530456</v>
+        <v>0.318547725271222</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8271</v>
+        <v>8390</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>404.4714575063144</v>
+        <v>406.3323950058719</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>193</v>
+        <v>109</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>41.44667373037303</v>
+        <v>47.0745128137694</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>19.39721573643367</v>
+        <v>21.19482262142719</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.7817084913805585</v>
+        <v>0.420501989814022</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-1.696032737125472</v>
+        <v>-1.100709063530456</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8464</v>
+        <v>8271</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>399.9736904564375</v>
+        <v>404.4714575063144</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>369</v>
+        <v>193</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>61.97204728945977</v>
+        <v>41.44667373037303</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>20.56965443893917</v>
+        <v>19.39721573643367</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.7537301662974047</v>
+        <v>0.7817084913805585</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>2.632811449359866</v>
+        <v>-1.696032737125472</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>9908</v>
+        <v>8464</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>大台北</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>390.0586603453077</v>
+        <v>399.9736904564375</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>29.8</v>
+        <v>369</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>58.53452209704864</v>
+        <v>61.97204728945977</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>19.61083746932587</v>
+        <v>20.56965443893917</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>2.030445432591359</v>
+        <v>0.7537301662974047</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.0165245061342178</v>
+        <v>2.632811449359866</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>9906</v>
+        <v>9908</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>欣巴巴</t>
+          <t>大台北</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>389.9291023832445</v>
+        <v>390.0586603453077</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>42.5</v>
+        <v>29.8</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>54.29774982524568</v>
+        <v>58.53452209704864</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>36.57179225949919</v>
+        <v>19.61083746932587</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.3028186906261348</v>
+        <v>2.030445432591359</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.4140455826464495</v>
+        <v>0.0165245061342178</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8341</v>
+        <v>9906</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>欣巴巴</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>373.9806614281228</v>
+        <v>389.9291023832445</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>77.09999999999999</v>
+        <v>42.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>46.67024210515729</v>
+        <v>54.29774982524568</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>21.76738649833271</v>
+        <v>36.57179225949919</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.8732809687291572</v>
+        <v>0.3028186906261348</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.4909772583657357</v>
+        <v>-0.4140455826464495</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>8147</v>
+        <v>8341</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>369.9988835341004</v>
+        <v>373.9806614281228</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>156</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>53.8573045053312</v>
+        <v>46.67024210515729</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>19.25739993762325</v>
+        <v>21.76738649833271</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.4719538596776</v>
+        <v>0.8732809687291572</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>1.614234845316472</v>
+        <v>-0.4909772583657357</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8102</v>
+        <v>8147</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>366.0677297333878</v>
+        <v>369.9988835341004</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>67.8</v>
+        <v>156</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>44.27328038657875</v>
+        <v>53.8573045053312</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>16.07371845212621</v>
+        <v>19.25739993762325</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.4275041948849122</v>
+        <v>1.4719538596776</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.7399004180981261</v>
+        <v>1.614234845316472</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8103</v>
+        <v>8102</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>365.268997109827</v>
+        <v>366.0677297333878</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>104</v>
+        <v>67.8</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>54.80697308844869</v>
+        <v>44.27328038657875</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>15.33082726307529</v>
+        <v>16.07371845212621</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.7029315383189157</v>
+        <v>0.4275041948849122</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>1.062654109863001</v>
+        <v>-0.7399004180981261</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8080</v>
+        <v>8103</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>345.187638016391</v>
+        <v>365.268997109827</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>49.12924499120602</v>
+        <v>54.80697308844869</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>46.56371979548452</v>
+        <v>15.33082726307529</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.482437912320697</v>
+        <v>0.7029315383189157</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0201903862221519</v>
+        <v>1.062654109863001</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8084</v>
+        <v>8080</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>巨虹</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>336.1382315770983</v>
+        <v>345.187638016391</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>48.9</v>
+        <v>28</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>54.10932674021821</v>
+        <v>49.12924499120602</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>18.1357182024017</v>
+        <v>46.56371979548452</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.285385885383786</v>
+        <v>1.482437912320697</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.0728777959590747</v>
+        <v>-0.0201903862221519</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>8104</v>
+        <v>8084</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>巨虹</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>336.0809840243252</v>
+        <v>336.1382315770983</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>38.05</v>
+        <v>48.9</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>47.32402908708712</v>
+        <v>54.10932674021821</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>19.57029434389487</v>
+        <v>18.1357182024017</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.2247215108697283</v>
+        <v>0.285385885383786</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.4536186407555864</v>
+        <v>-0.0728777959590747</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8299</v>
+        <v>8104</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>332.0032276955285</v>
+        <v>336.0809840243252</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>2295</v>
+        <v>38.05</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>46.70673881384168</v>
+        <v>47.32402908708712</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>12.14125663994801</v>
+        <v>19.57029434389487</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.5941152987213513</v>
+        <v>0.2247215108697283</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-23.3299099218222</v>
+        <v>-0.4536186407555864</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>8440</v>
+        <v>8299</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>318.6068687205237</v>
+        <v>332.0032276955285</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>21.85</v>
+        <v>2295</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>47.60578101423177</v>
+        <v>46.70673881384168</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>10.06595214031038</v>
+        <v>12.14125663994801</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.069237711078173</v>
+        <v>0.5941152987213513</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.0458378570134953</v>
+        <v>-23.3299099218222</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>9955</v>
+        <v>8440</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>317.1490079045574</v>
+        <v>318.6068687205237</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>27.05</v>
+        <v>21.85</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>47.32391000825986</v>
+        <v>47.60578101423177</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>22.72253157493418</v>
+        <v>10.06595214031038</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.708657202072157</v>
+        <v>1.069237711078173</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.07278279382103101</v>
+        <v>-0.0458378570134953</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>8431</v>
+        <v>9955</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>310.1753637979651</v>
+        <v>317.1490079045574</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>52.3</v>
+        <v>27.05</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>44.04258024390843</v>
+        <v>47.32391000825986</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>11.25468054755357</v>
+        <v>22.72253157493418</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.3102073942355585</v>
+        <v>1.708657202072157</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.1249647775964251</v>
+        <v>0.07278279382103101</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>8101</v>
+        <v>8431</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>309.1606062310391</v>
+        <v>310.1753637979651</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>13.6</v>
+        <v>52.3</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>46.79113799814321</v>
+        <v>44.04258024390843</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>12.89863303428128</v>
+        <v>11.25468054755357</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>3.306539289441168</v>
+        <v>0.3102073942355585</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.1857960687241316</v>
+        <v>0.1249647775964251</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8048</v>
+        <v>8101</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>303.0249388739218</v>
+        <v>309.1606062310391</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>62.7</v>
+        <v>13.6</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>48.40032175702248</v>
+        <v>46.79113799814321</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>13.75009366597453</v>
+        <v>12.89863303428128</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.4104276843743</v>
+        <v>3.306539289441168</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.4001217864231792</v>
+        <v>-0.1857960687241316</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>9930</v>
+        <v>8048</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>299.7191203601428</v>
+        <v>303.0249388739218</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>64.7</v>
+        <v>62.7</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>23.73874756085995</v>
+        <v>48.40032175702248</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>30.65727319082356</v>
+        <v>13.75009366597453</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>2.174704971503587</v>
+        <v>0.4104276843743</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.4392204029982234</v>
+        <v>-0.4001217864231792</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>8176</v>
+        <v>9930</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>292.9792362513791</v>
+        <v>299.7191203601428</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>10.7</v>
+        <v>64.7</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>61.07721924103758</v>
+        <v>23.73874756085995</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>16.40646245759422</v>
+        <v>30.65727319082356</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.309761635416918</v>
+        <v>2.174704971503587</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.0828849191126893</v>
+        <v>-0.4392204029982234</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8404</v>
+        <v>8176</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>291.6001789913028</v>
+        <v>292.9792362513791</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>17</v>
+        <v>10.7</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>53.79075289195699</v>
+        <v>61.07721924103758</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>12.12254973161458</v>
+        <v>16.40646245759422</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.473617656974669</v>
+        <v>1.309761635416918</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0211036033750372</v>
+        <v>0.0828849191126893</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, kd_golden_cross</t>
+          <t>rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8478</v>
+        <v>8404</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>285.6667990228493</v>
+        <v>291.6001789913028</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>160</v>
+        <v>17</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>58.20555906266884</v>
+        <v>53.79075289195699</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>13.06003371891715</v>
+        <v>12.12254973161458</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.879580162870564</v>
+        <v>1.473617656974669</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.8658035957982528</v>
+        <v>0.0211036033750372</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>8367</v>
+        <v>8478</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>275.9622399839657</v>
+        <v>285.6667990228493</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>40.25</v>
+        <v>160</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>43.6513503362529</v>
+        <v>58.20555906266884</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>23.06022565204979</v>
+        <v>13.06003371891715</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.373303847413244</v>
+        <v>1.879580162870564</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0553259209561237</v>
+        <v>0.8658035957982528</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8213</v>
+        <v>8367</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>271.1088993278752</v>
+        <v>275.9622399839657</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>36.2</v>
+        <v>40.25</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>46.88813390292509</v>
+        <v>43.6513503362529</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>12.29871079510948</v>
+        <v>23.06022565204979</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.533367655788676</v>
+        <v>1.373303847413244</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.0292110785576579</v>
+        <v>0.0553259209561237</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8482</v>
+        <v>8213</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>270.8206319139388</v>
+        <v>271.1088993278752</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>48.05</v>
+        <v>36.2</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>51.57830060679604</v>
+        <v>46.88813390292509</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>7.334338121492368</v>
+        <v>12.29871079510948</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5795589556347619</v>
+        <v>0.533367655788676</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>1.952750067332031</v>
+        <v>-0.0292110785576579</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8423</v>
+        <v>8482</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>259.7568339272046</v>
+        <v>270.8206319139388</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>17.85</v>
+        <v>48.05</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>53.57235599105236</v>
+        <v>51.57830060679604</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>9.8193208420765</v>
+        <v>7.334338121492368</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.4744782935429794</v>
+        <v>0.5795589556347619</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0070224767724646</v>
+        <v>1.952750067332031</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>9910</v>
+        <v>8423</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>256.7835444591468</v>
+        <v>259.7568339272046</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>68.59999999999999</v>
+        <v>17.85</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>41.60477883081496</v>
+        <v>53.57235599105236</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>19.13070530879997</v>
+        <v>9.8193208420765</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.33858442573219</v>
+        <v>0.4744782935429794</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-1.103674648023966</v>
+        <v>0.0070224767724646</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8472</v>
+        <v>9910</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>249.5928403911192</v>
+        <v>256.7835444591468</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>82.90000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>50.8420774280016</v>
+        <v>41.60477883081496</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>16.80553485527012</v>
+        <v>19.13070530879997</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.117090113506883</v>
+        <v>0.33858442573219</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-1.007314961441882</v>
+        <v>-1.103674648023966</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8068</v>
+        <v>8472</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>245.5094796071398</v>
+        <v>249.5928403911192</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>19.45</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>49.53066053959586</v>
+        <v>50.8420774280016</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>17.54539990450208</v>
+        <v>16.80553485527012</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.7418021579914481</v>
+        <v>0.117090113506883</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.127445136830401</v>
+        <v>-1.007314961441882</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8087</v>
+        <v>8068</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>237.6947043483567</v>
+        <v>245.5094796071398</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>31.5</v>
+        <v>19.45</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>37.53234040539925</v>
+        <v>49.53066053959586</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>12.245129678211</v>
+        <v>17.54539990450208</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>2.480425600109891</v>
+        <v>0.7418021579914481</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.2305635137802408</v>
+        <v>0.127445136830401</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>9907</v>
+        <v>8087</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>統一實</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>232.3450643563041</v>
+        <v>237.6947043483567</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>15.55</v>
+        <v>31.5</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>43.97657455471278</v>
+        <v>37.53234040539925</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>27.97809536607498</v>
+        <v>12.245129678211</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.8315318464393294</v>
+        <v>2.480425600109891</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.0324601636710516</v>
+        <v>-0.2305635137802408</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8089</v>
+        <v>9907</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>統一實</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>232.1029813581443</v>
+        <v>232.3450643563041</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>20.25</v>
+        <v>15.55</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>47.60430761004748</v>
+        <v>43.97657455471278</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>28.78410714511095</v>
+        <v>27.97809536607498</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.4341962411825692</v>
+        <v>0.8315318464393294</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0519833256941696</v>
+        <v>-0.0324601636710516</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>9103</v>
+        <v>8089</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>226.4474722339818</v>
+        <v>232.1029813581443</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>5.27</v>
+        <v>20.25</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>49.45447831418948</v>
+        <v>47.60430761004748</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>18.3789477782442</v>
+        <v>28.78410714511095</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.3354250752485433</v>
+        <v>0.4341962411825692</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.0421952811631571</v>
+        <v>-0.0519833256941696</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>8477</v>
+        <v>9103</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>222.8898244909818</v>
+        <v>226.4474722339818</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>16.1</v>
+        <v>5.27</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>42.50586434531409</v>
+        <v>49.45447831418948</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>18.76705652402952</v>
+        <v>18.3789477782442</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.5156621476282124</v>
+        <v>0.3354250752485433</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.2308271527890275</v>
+        <v>-0.0421952811631571</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>8455</v>
+        <v>8477</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>219.6248676311364</v>
+        <v>222.8898244909818</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>28.8</v>
+        <v>16.1</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>45.04239471825338</v>
+        <v>42.50586434531409</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>18.2310941116387</v>
+        <v>18.76705652402952</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.1806626831866657</v>
+        <v>0.5156621476282124</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.2855821631667814</v>
+        <v>-0.2308271527890275</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8067</v>
+        <v>8455</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>214.2968210619757</v>
+        <v>219.6248676311364</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>13.45</v>
+        <v>28.8</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>52.30181234243322</v>
+        <v>45.04239471825338</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>7.766732612185899</v>
+        <v>18.2310941116387</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.1954018778310929</v>
+        <v>0.1806626831866657</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0422657527627221</v>
+        <v>-0.2855821631667814</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>8249</v>
+        <v>8067</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>志旭</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>210.4062125717864</v>
+        <v>214.2968210619757</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>49.1</v>
+        <v>13.45</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>44.93693759047076</v>
+        <v>52.30181234243322</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>15.96189512950526</v>
+        <v>7.766732612185899</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.5226407335735586</v>
+        <v>0.1954018778310929</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.2792733485482879</v>
+        <v>-0.0422657527627221</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8114</v>
+        <v>8249</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>209.3026927905396</v>
+        <v>210.4062125717864</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>203</v>
+        <v>49.1</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>48.45903754337948</v>
+        <v>44.93693759047076</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>20.59774793810952</v>
+        <v>15.96189512950526</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.7027606675679744</v>
+        <v>0.5226407335735586</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-1.318812415093302</v>
+        <v>-0.2792733485482879</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>8210</v>
+        <v>8114</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>194.0566421622165</v>
+        <v>209.3026927905396</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>1305</v>
+        <v>203</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>47.49545954329742</v>
+        <v>48.45903754337948</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>14.53755287290162</v>
+        <v>20.59774793810952</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.4666579081414472</v>
+        <v>0.7027606675679744</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-10.54479000922738</v>
+        <v>-1.318812415093302</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>9904</v>
+        <v>8210</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>190.3065161032508</v>
+        <v>194.0566421622165</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>24.45</v>
+        <v>1305</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>31.91131540309871</v>
+        <v>47.49545954329742</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>19.81251015878305</v>
+        <v>14.53755287290162</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.930651610325084</v>
+        <v>0.4666579081414472</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.19028531885098</v>
+        <v>-10.54479000922738</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>9110</v>
+        <v>9904</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>183.6442097875548</v>
+        <v>190.3065161032508</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>3.2</v>
+        <v>24.45</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>51.18744866726711</v>
+        <v>31.91131540309871</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>13.93811642617339</v>
+        <v>19.81251015878305</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.3248629194502391</v>
+        <v>0.930651610325084</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0478386725285678</v>
+        <v>-0.19028531885098</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>8940</v>
+        <v>9110</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>176.5403970792684</v>
+        <v>183.6442097875548</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>16.6</v>
+        <v>3.2</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>47.04918820120118</v>
+        <v>51.18744866726711</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>16.98314198325689</v>
+        <v>13.93811642617339</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.119430684087313</v>
+        <v>0.3248629194502391</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.0282492217278898</v>
+        <v>0.0478386725285678</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>8463</v>
+        <v>8940</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>170.5764261286687</v>
+        <v>176.5403970792684</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>21.55</v>
+        <v>16.6</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>47.08877920412657</v>
+        <v>47.04918820120118</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>14.18982820358816</v>
+        <v>16.98314198325689</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.9453915232693616</v>
+        <v>1.119430684087313</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.0062429750459777</v>
+        <v>0.0282492217278898</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8059</v>
+        <v>8463</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>145.1343246041251</v>
+        <v>170.5764261286687</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>16.75</v>
+        <v>21.55</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>38.99819314702025</v>
+        <v>47.08877920412657</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>22.99389465658838</v>
+        <v>14.18982820358816</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.6559824844940475</v>
+        <v>0.9453915232693616</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.02350379403917</v>
+        <v>-0.0062429750459777</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>9802</v>
+        <v>8059</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>鈺齊-KY</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>114.7340309801021</v>
+        <v>145.1343246041251</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>74.40000000000001</v>
+        <v>16.75</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>44.82036260790606</v>
+        <v>38.99819314702025</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>16.99112605495807</v>
+        <v>22.99389465658838</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.6524151173002712</v>
+        <v>0.6559824844940475</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.3167149437502894</v>
+        <v>-0.02350379403917</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>8410</v>
+        <v>9802</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>鈺齊-KY</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>92.66557033269694</v>
+        <v>114.7340309801021</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>33</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>41.48524205258757</v>
+        <v>44.82036260790606</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>17.5145651084731</v>
+        <v>16.99112605495807</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.011562781339577</v>
+        <v>0.6524151173002712</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.0880773152492651</v>
+        <v>-0.3167149437502894</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>8487</v>
+        <v>8410</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>森田</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>84.86643380774051</v>
+        <v>92.66557033269694</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>78.3</v>
+        <v>33</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>46.36265236860265</v>
+        <v>41.48524205258757</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>11.17311210762735</v>
+        <v>17.5145651084731</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.4042967774169373</v>
+        <v>1.011562781339577</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.1628601413540077</v>
+        <v>0.0880773152492651</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6463,21 +6463,21 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>8429</v>
+        <v>8487</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>83.37815752972179</v>
+        <v>84.86643380774051</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>6.48</v>
+        <v>78.3</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>54.34243348225099</v>
+        <v>46.36265236860265</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>16.9217956276988</v>
+        <v>11.17311210762735</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.554578528557812</v>
+        <v>0.4042967774169373</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.0135443401315418</v>
+        <v>-0.1628601413540077</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>8467</v>
+        <v>8429</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>72.17795299795885</v>
+        <v>83.37815752972179</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>113</v>
+        <v>6.48</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>46.5388319071177</v>
+        <v>54.34243348225099</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>10.71158050236279</v>
+        <v>16.9217956276988</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.8862616622747668</v>
+        <v>1.554578528557812</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,62 +6559,115 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.1578101323085738</v>
+        <v>-0.0135443401315418</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
+        <v>8467</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>波力-KY</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>72.17795299795885</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>46.5388319071177</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>10.71158050236279</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.8862616622747668</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>0.1578101323085738</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
         <v>8085</v>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>福華</t>
         </is>
       </c>
-      <c r="C116" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D116" s="2" t="n">
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
         <v>0.5086503422807063</v>
       </c>
-      <c r="E116" s="2" t="n">
+      <c r="E117" s="2" t="n">
         <v>12.25</v>
       </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H116" s="2" t="n">
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
         <v>47.61954649847997</v>
       </c>
-      <c r="I116" s="2" t="n">
+      <c r="I117" s="2" t="n">
         <v>16.67836063418679</v>
       </c>
-      <c r="J116" s="2" t="n">
+      <c r="J117" s="2" t="n">
         <v>0.4173626216301453</v>
       </c>
-      <c r="K116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M116" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N116" s="2" t="n">
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
         <v>-0.0528102175679734</v>
       </c>
-      <c r="O116" s="2" t="inlineStr">
+      <c r="O117" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60</t>
         </is>
